--- a/Codelist Excel Files and Conversion Templates to XML/installationMethod.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/installationMethod.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes classifying a rigid inclusion installation method by soil-displacement behaviour - whether the technique pushes soil aside, removes it, or something between - distinct from diggs:RigidInclusionType/columnType, which names the rig/technique family rather than its displacement behaviour. Used for the value of diggs:RIConstructionActivityType/diggs:installationMethod.</t>
+          <t>Codes classifying a rigid inclusion installation method by soil-displacement behaviour - whether the technique pushes soil aside, removes it, or something between - distinct from diggs:RIColumnType/columnType, which names the rig/technique family rather than its displacement behaviour. Used for the value of diggs:RIConstructionActivityType/diggs:installationMethod.</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/installationMethod.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/installationMethod.xlsx
@@ -1087,7 +1087,7 @@
       </c>
       <c r="D2" s="14" t="inlineStr">
         <is>
-          <t>A continuous-flight or displacement auger that advances by pushing soil radially outward with no spoil removal, densifying and laterally stressing the surrounding ground as it penetrates.</t>
+          <t>A continuous-flight or displacement auger that advances by pushing soil radially outward with no spoil removal, densifying and laterally stressing the surrounding ground as it penetrates. Displacement family: soil is displaced laterally rather than removed, so no spoil is generated.</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>A method that removes some spoil while displacing the remainder, an intermediate case between full displacement and pre-drill/spoil removal.</t>
+          <t>A method that removes some spoil while displacing the remainder, an intermediate case between full displacement and pre-drill/spoil removal. Intermediate between the displacement and replacement families.</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A displacement tool advanced with a drilling (rotary) action rather than pure static push, combining drilling penetration with lateral soil displacement.</t>
+          <t>A displacement tool advanced with a drilling (rotary) action rather than pure static push, combining drilling penetration with lateral soil displacement. Displacement family: soil is displaced laterally rather than removed, so no spoil is generated. Trade names in common use: Controlled Modulus Column (CMC, Menard); and Rigid Inclusion (RI), also marketed as GI, GeoConcrete Column (GCC), Controlled Stiffness Column (CSC) and Augered Pressure Grout Column (APGC) by Keller / Hayward Baker.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>The hole is pre-drilled and spoil removed before or during grout placement, with no net soil displacement into the surrounding ground.</t>
+          <t>The hole is pre-drilled and spoil removed before or during grout placement, with no net soil displacement into the surrounding ground. Replacement family: soil is removed as the column is formed.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -1202,10 +1202,31 @@
         <f>IF(ISNA(VLOOKUP(B6,AssociatedElements!B$2:B2944,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="G6" s="9" t="n"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>vibratory_displacement</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Vibratory displacement</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>A displacement method in which the tool is advanced by vibration rather than by rotary drilling or static push. Offered by Keller / Hayward Baker alongside single-pass augering. Displacement family: soil is displaced laterally rather than removed, so no spoil is generated.</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2">
@@ -1671,7 +1692,16 @@
         <f>IF(ISNA(VLOOKUP(B6,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>vibratory_displacement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>//diggs:RIConstructionActivity/diggs:installationMethod</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
